--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34527,6 +34527,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1486">
+      <c r="A1486" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1486" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G1486" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34550,6 +34550,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1487">
+      <c r="A1487" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1487" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G1487" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1488" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C1488" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="G1488" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34596,6 +34596,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1489" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34437,22 +34437,22 @@
     </row>
     <row r="1482">
       <c r="A1482" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1482" t="n">
-        <v>14000</v>
+        <v>12800</v>
       </c>
       <c r="C1482" t="n">
-        <v>1.36000001430511</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="D1482" t="n">
-        <v>1.24000000953674</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="E1482" t="n">
-        <v>1.24000000953674</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="F1482" t="n">
-        <v>1.3400000333786</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="G1482" t="s">
         <v>7</v>
@@ -34460,22 +34460,22 @@
     </row>
     <row r="1483">
       <c r="A1483" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1483" t="n">
-        <v>6400</v>
+        <v>14000</v>
       </c>
       <c r="C1483" t="n">
-        <v>1.2849999666214</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="D1483" t="n">
-        <v>1.20000004768372</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="E1483" t="n">
-        <v>1.2849999666214</v>
+        <v>1.24000000953674</v>
       </c>
       <c r="F1483" t="n">
-        <v>1.20000004768372</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="G1483" t="s">
         <v>7</v>
@@ -34483,22 +34483,22 @@
     </row>
     <row r="1484">
       <c r="A1484" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1484" t="n">
-        <v>10000</v>
+        <v>6400</v>
       </c>
       <c r="C1484" t="n">
-        <v>1.17999994754791</v>
+        <v>1.2849999666214</v>
       </c>
       <c r="D1484" t="n">
-        <v>1.14999997615814</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E1484" t="n">
-        <v>1.17999994754791</v>
+        <v>1.2849999666214</v>
       </c>
       <c r="F1484" t="n">
-        <v>1.16999995708466</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G1484" t="s">
         <v>7</v>
@@ -34506,19 +34506,19 @@
     </row>
     <row r="1485">
       <c r="A1485" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1485" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="C1485" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="D1485" t="n">
-        <v>1.16999995708466</v>
+        <v>1.14999997615814</v>
       </c>
       <c r="E1485" t="n">
-        <v>1.16999995708466</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="F1485" t="n">
         <v>1.16999995708466</v>
@@ -34529,10 +34529,10 @@
     </row>
     <row r="1486">
       <c r="A1486" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1486" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C1486" t="n">
         <v>1.16999995708466</v>
@@ -34552,7 +34552,7 @@
     </row>
     <row r="1487">
       <c r="A1487" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1487" t="n">
         <v>0</v>
@@ -34575,22 +34575,22 @@
     </row>
     <row r="1488">
       <c r="A1488" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1488" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="C1488" t="n">
-        <v>1.14999997615814</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="D1488" t="n">
-        <v>1.14499998092651</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E1488" t="n">
-        <v>1.14999997615814</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="F1488" t="n">
-        <v>1.14499998092651</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="G1488" t="s">
         <v>7</v>
@@ -34598,24 +34598,47 @@
     </row>
     <row r="1489">
       <c r="A1489" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1489" t="n">
-        <v>4800</v>
+        <v>8400</v>
       </c>
       <c r="C1489" t="n">
-        <v>1.16999995708466</v>
+        <v>1.14999997615814</v>
       </c>
       <c r="D1489" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1490" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1490" t="n">
         <v>1.12999999523163</v>
       </c>
-      <c r="E1489" t="n">
-        <v>1.13999998569489</v>
-      </c>
-      <c r="F1489" t="n">
+      <c r="D1490" t="n">
         <v>1.12999999523163</v>
       </c>
-      <c r="G1489" t="s">
+      <c r="E1490" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="G1490" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39152,7 +39152,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="D1492" t="n">
-        <v>1.14999997615814</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="E1492" t="n">
         <v>1.14999997615814</v>
@@ -39164,6 +39164,32 @@
         <v>1.11500000953674</v>
       </c>
       <c r="H1492" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1493" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1493" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="H1493" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39193,6 +39193,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1494" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1494" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="H1494" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39219,6 +39219,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1495" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1495" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H1495" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39245,6 +39245,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="H1496" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39323,6 +39323,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="H1499" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34895,6 +34895,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1502" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1503"/>
+      <c r="G1503" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34934,8 +34934,31 @@
       <c r="E1503" t="n">
         <v>0.899999976158142</v>
       </c>
-      <c r="F1503"/>
+      <c r="F1503" t="n">
+        <v>0.899999976158142</v>
+      </c>
       <c r="G1503" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="F1504"/>
+      <c r="G1504" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34957,7 +34957,9 @@
       <c r="E1504" t="n">
         <v>0.864000022411346</v>
       </c>
-      <c r="F1504"/>
+      <c r="F1504" t="n">
+        <v>0.864000022411346</v>
+      </c>
       <c r="G1504" t="s">
         <v>7</v>
       </c>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -34964,6 +34964,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="G1505" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1506"/>
+      <c r="G1506" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -35010,6 +35010,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>30400</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>0.857999980449677</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="G1507" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -39609,6 +39609,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1510" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1510" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="H1510" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44197,6 +44197,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1512">
+      <c r="A1512" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1512" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1512" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>0.762000024318695</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>10800</v>
+      </c>
+      <c r="I1512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1513" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>0.765999972820282</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I1513" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44255,6 +44255,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1514">
+      <c r="A1514" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1514" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I1514" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44284,6 +44284,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1515">
+      <c r="A1515" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1515" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1515" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I1515" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44313,6 +44313,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1516">
+      <c r="A1516" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1516" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I1516" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44342,6 +44342,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1517">
+      <c r="A1517" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1517" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1518" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>800</v>
+      </c>
+      <c r="I1518" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44400,6 +44400,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1519">
+      <c r="A1519" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1519" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1519" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TCM.MI.xlsx
+++ b/data/TCM.MI.xlsx
@@ -44429,6 +44429,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1520">
+      <c r="A1520" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1520" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>0.744000017642975</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1520" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
